--- a/DRMLT_Indicadores-desempenho_Final.xlsx
+++ b/DRMLT_Indicadores-desempenho_Final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://governosp.sharepoint.com/teams/DETRAN-CoordenadoriadeSeguranaViria/Shared Documents/DSV-CGSV - COST - DRML/3. Produção/1. Projetos Estratégicos/1. PSV/2. Monitoramento/9. Painel/Bases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="530" documentId="11_4BC2B58C6C7465FBB268A2EBDBB67864AD078E98" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D38949D-89DD-442F-958D-EB88EB317EC2}"/>
+  <xr:revisionPtr revIDLastSave="663" documentId="11_4BC2B58C6C7465FBB268A2EBDBB67864AD078E98" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{565DDE9F-2EE7-4510-9AE9-B9DAE8279EB0}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="945" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicadores de desempenho" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="328">
   <si>
     <t>O que mede</t>
   </si>
@@ -983,17 +983,91 @@
   <si>
     <t>Atendimento às vítimas</t>
   </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>7.1</t>
+  </si>
+  <si>
+    <t>7.2</t>
+  </si>
+  <si>
+    <t>7.3</t>
+  </si>
+  <si>
+    <t>8.1</t>
+  </si>
+  <si>
+    <t>8.2</t>
+  </si>
+  <si>
+    <t>8.3</t>
+  </si>
+  <si>
+    <t>8.4</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="d\.m"/>
+  <numFmts count="2">
     <numFmt numFmtId="165" formatCode="[$R$ -416]#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1021,6 +1095,18 @@
       <color theme="1"/>
       <name val="Open Sans"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1125,7 +1211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1142,9 +1228,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1159,9 +1242,6 @@
     </xf>
     <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1217,17 +1297,11 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1465,22 +1539,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>291</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="18" t="s">
         <v>292</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="18" t="s">
         <v>293</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="18" t="s">
         <v>278</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="15" t="s">
         <v>290</v>
       </c>
       <c r="G1" s="5" t="s">
@@ -1492,3907 +1566,3907 @@
       <c r="I1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="K1" s="19" t="s">
         <v>277</v>
       </c>
-      <c r="L1" s="21" t="s">
+      <c r="L1" s="19" t="s">
         <v>280</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="M1" s="19" t="s">
         <v>279</v>
       </c>
-      <c r="N1" s="21" t="s">
+      <c r="N1" s="19" t="s">
         <v>281</v>
       </c>
-      <c r="O1" s="21" t="s">
+      <c r="O1" s="19" t="s">
         <v>283</v>
       </c>
-      <c r="P1" s="21" t="s">
+      <c r="P1" s="19" t="s">
         <v>285</v>
       </c>
-      <c r="Q1" s="22" t="s">
+      <c r="Q1" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="R1" s="22" t="s">
+      <c r="R1" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="S1" s="23" t="s">
+      <c r="S1" s="21" t="s">
         <v>288</v>
       </c>
-      <c r="T1" s="23" t="s">
+      <c r="T1" s="21" t="s">
         <v>289</v>
       </c>
-      <c r="U1" s="23" t="s">
+      <c r="U1" s="21" t="s">
         <v>286</v>
       </c>
       <c r="V1" s="1"/>
     </row>
     <row r="2" spans="1:22" ht="153" x14ac:dyDescent="0.2">
-      <c r="A2" s="19">
+      <c r="A2" s="17">
         <v>1</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="29" t="s">
         <v>295</v>
       </c>
-      <c r="C2" s="31">
-        <v>45658</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="C2" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="24">
+      <c r="K2" s="22">
         <f>1/2</f>
         <v>0.5</v>
       </c>
-      <c r="L2" s="24">
+      <c r="L2" s="22">
         <f>1/3</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M2" s="24">
+      <c r="M2" s="22">
         <f>1/8</f>
         <v>0.125</v>
       </c>
-      <c r="N2" s="24">
+      <c r="N2" s="22">
         <f>K2*L2*M2</f>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O2" s="24">
-        <v>100</v>
-      </c>
-      <c r="P2" s="25">
+      <c r="O2" s="22">
+        <v>10</v>
+      </c>
+      <c r="P2" s="23">
         <f>N2*O2</f>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q2" s="24">
+        <v>0.20833333333333331</v>
+      </c>
+      <c r="Q2" s="22">
         <f>1/51</f>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R2" s="27">
+      <c r="R2" s="25">
         <f>Q2*O2</f>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S2" s="24">
+        <v>0.19607843137254902</v>
+      </c>
+      <c r="S2" s="22">
         <f>7/8</f>
         <v>0.875</v>
       </c>
-      <c r="T2" s="24">
+      <c r="T2" s="22">
         <f>S2/$S$53</f>
         <v>3.017241379310345E-2</v>
       </c>
-      <c r="U2" s="29">
+      <c r="U2" s="27">
         <f>T2*O2</f>
-        <v>3.0172413793103448</v>
+        <v>0.30172413793103448</v>
       </c>
       <c r="V2" s="2"/>
     </row>
     <row r="3" spans="1:22" ht="165.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="19">
+      <c r="A3" s="17">
         <v>1</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="29" t="s">
         <v>295</v>
       </c>
-      <c r="C3" s="31">
-        <v>45658</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="22">
         <f>1/2</f>
         <v>0.5</v>
       </c>
-      <c r="L3" s="24">
+      <c r="L3" s="22">
         <f t="shared" ref="L3:L45" si="0">1/3</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M3" s="24">
+      <c r="M3" s="22">
         <f t="shared" ref="M3:M52" si="1">1/8</f>
         <v>0.125</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="22">
         <f t="shared" ref="N3:N52" si="2">K3*L3*M3</f>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O3" s="24">
-        <v>100</v>
-      </c>
-      <c r="P3" s="25">
+      <c r="O3" s="22">
+        <v>15</v>
+      </c>
+      <c r="P3" s="23">
         <f t="shared" ref="P3:P52" si="3">N3*O3</f>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q3" s="24">
+        <v>0.3125</v>
+      </c>
+      <c r="Q3" s="22">
         <f t="shared" ref="Q3:Q52" si="4">1/51</f>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R3" s="27">
+      <c r="R3" s="25">
         <f t="shared" ref="R3:R52" si="5">Q3*O3</f>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S3" s="24">
+        <v>0.29411764705882354</v>
+      </c>
+      <c r="S3" s="22">
         <f t="shared" ref="S3:S7" si="6">7/8</f>
         <v>0.875</v>
       </c>
-      <c r="T3" s="24">
+      <c r="T3" s="22">
         <f t="shared" ref="T3:T52" si="7">S3/$S$53</f>
         <v>3.017241379310345E-2</v>
       </c>
-      <c r="U3" s="29">
+      <c r="U3" s="27">
         <f t="shared" ref="U3:U52" si="8">T3*O3</f>
-        <v>3.0172413793103448</v>
+        <v>0.45258620689655177</v>
       </c>
       <c r="V3" s="2"/>
     </row>
     <row r="4" spans="1:22" ht="153" x14ac:dyDescent="0.2">
-      <c r="A4" s="19">
+      <c r="A4" s="17">
         <v>1</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="29" t="s">
         <v>295</v>
       </c>
-      <c r="C4" s="31">
-        <v>45689</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="30" t="s">
+        <v>304</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="24">
+      <c r="K4" s="22">
         <f t="shared" ref="K4:K52" si="9">1/2</f>
         <v>0.5</v>
       </c>
-      <c r="L4" s="24">
+      <c r="L4" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M4" s="24">
+      <c r="M4" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N4" s="24">
+      <c r="N4" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O4" s="24">
-        <v>100</v>
-      </c>
-      <c r="P4" s="25">
+      <c r="O4" s="22">
+        <v>20</v>
+      </c>
+      <c r="P4" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q4" s="24">
+        <v>0.41666666666666663</v>
+      </c>
+      <c r="Q4" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R4" s="27">
+      <c r="R4" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S4" s="24">
+        <v>0.39215686274509803</v>
+      </c>
+      <c r="S4" s="22">
         <f t="shared" si="6"/>
         <v>0.875</v>
       </c>
-      <c r="T4" s="24">
+      <c r="T4" s="22">
         <f t="shared" si="7"/>
         <v>3.017241379310345E-2</v>
       </c>
-      <c r="U4" s="29">
+      <c r="U4" s="27">
         <f t="shared" si="8"/>
-        <v>3.0172413793103448</v>
+        <v>0.60344827586206895</v>
       </c>
       <c r="V4" s="2"/>
     </row>
     <row r="5" spans="1:22" ht="113.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="19">
+      <c r="A5" s="17">
         <v>1</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="29" t="s">
         <v>295</v>
       </c>
-      <c r="C5" s="31">
-        <v>45689</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="C5" s="30" t="s">
+        <v>304</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="24">
+      <c r="K5" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L5" s="24">
+      <c r="L5" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M5" s="24">
+      <c r="M5" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N5" s="24">
+      <c r="N5" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O5" s="24">
-        <v>100</v>
-      </c>
-      <c r="P5" s="25">
+      <c r="O5" s="22">
+        <v>1</v>
+      </c>
+      <c r="P5" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q5" s="24">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="Q5" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R5" s="27">
+      <c r="R5" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S5" s="24">
+        <v>1.9607843137254902E-2</v>
+      </c>
+      <c r="S5" s="22">
         <f t="shared" si="6"/>
         <v>0.875</v>
       </c>
-      <c r="T5" s="24">
+      <c r="T5" s="22">
         <f t="shared" si="7"/>
         <v>3.017241379310345E-2</v>
       </c>
-      <c r="U5" s="29">
+      <c r="U5" s="27">
         <f t="shared" si="8"/>
-        <v>3.0172413793103448</v>
+        <v>3.017241379310345E-2</v>
       </c>
       <c r="V5" s="2"/>
     </row>
     <row r="6" spans="1:22" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="19">
+      <c r="A6" s="17">
         <v>1</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="29" t="s">
         <v>295</v>
       </c>
-      <c r="C6" s="31">
-        <v>45717</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="C6" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="24">
+      <c r="K6" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L6" s="24">
+      <c r="L6" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M6" s="24">
+      <c r="M6" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N6" s="24">
+      <c r="N6" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O6" s="24">
-        <v>100</v>
-      </c>
-      <c r="P6" s="25">
+      <c r="O6" s="22">
+        <v>2</v>
+      </c>
+      <c r="P6" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q6" s="24">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="Q6" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R6" s="27">
+      <c r="R6" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S6" s="24">
+        <v>3.9215686274509803E-2</v>
+      </c>
+      <c r="S6" s="22">
         <f t="shared" si="6"/>
         <v>0.875</v>
       </c>
-      <c r="T6" s="24">
+      <c r="T6" s="22">
         <f t="shared" si="7"/>
         <v>3.017241379310345E-2</v>
       </c>
-      <c r="U6" s="29">
+      <c r="U6" s="27">
         <f t="shared" si="8"/>
-        <v>3.0172413793103448</v>
+        <v>6.0344827586206899E-2</v>
       </c>
       <c r="V6" s="2"/>
     </row>
     <row r="7" spans="1:22" ht="102" x14ac:dyDescent="0.2">
-      <c r="A7" s="19">
+      <c r="A7" s="17">
         <v>1</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="29" t="s">
         <v>295</v>
       </c>
-      <c r="C7" s="31">
-        <v>45717</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="C7" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K7" s="24">
+      <c r="K7" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L7" s="24">
+      <c r="L7" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M7" s="24">
+      <c r="M7" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N7" s="24">
+      <c r="N7" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O7" s="24">
-        <v>100</v>
-      </c>
-      <c r="P7" s="25">
+      <c r="O7" s="22">
+        <v>3</v>
+      </c>
+      <c r="P7" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q7" s="24">
+        <v>6.25E-2</v>
+      </c>
+      <c r="Q7" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R7" s="27">
+      <c r="R7" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S7" s="24">
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="S7" s="22">
         <f t="shared" si="6"/>
         <v>0.875</v>
       </c>
-      <c r="T7" s="24">
+      <c r="T7" s="22">
         <f t="shared" si="7"/>
         <v>3.017241379310345E-2</v>
       </c>
-      <c r="U7" s="29">
+      <c r="U7" s="27">
         <f t="shared" si="8"/>
-        <v>3.0172413793103448</v>
+        <v>9.0517241379310345E-2</v>
       </c>
       <c r="V7" s="2"/>
     </row>
     <row r="8" spans="1:22" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="19">
+      <c r="A8" s="17">
         <v>2</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="C8" s="31">
-        <v>45659</v>
-      </c>
-      <c r="D8" s="7" t="s">
+      <c r="C8" s="30" t="s">
+        <v>306</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K8" s="24">
+      <c r="K8" s="22">
         <f>1/3</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="L8" s="24">
+      <c r="L8" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M8" s="24">
+      <c r="M8" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N8" s="24">
+      <c r="N8" s="22">
         <f t="shared" si="2"/>
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="O8" s="24">
-        <v>100</v>
-      </c>
-      <c r="P8" s="25">
+      <c r="O8" s="22">
+        <v>0</v>
+      </c>
+      <c r="P8" s="23">
         <f t="shared" si="3"/>
-        <v>1.3888888888888888</v>
-      </c>
-      <c r="Q8" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R8" s="27">
+      <c r="R8" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S8" s="24">
+        <v>0</v>
+      </c>
+      <c r="S8" s="22">
         <f>4/8</f>
         <v>0.5</v>
       </c>
-      <c r="T8" s="24">
+      <c r="T8" s="22">
         <f t="shared" si="7"/>
         <v>1.7241379310344827E-2</v>
       </c>
-      <c r="U8" s="29">
+      <c r="U8" s="27">
         <f t="shared" si="8"/>
-        <v>1.7241379310344827</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2"/>
     </row>
     <row r="9" spans="1:22" ht="102" x14ac:dyDescent="0.2">
-      <c r="A9" s="19">
+      <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="C9" s="31">
-        <v>45659</v>
-      </c>
-      <c r="D9" s="7" t="s">
+      <c r="C9" s="30" t="s">
+        <v>306</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="J9" s="10" t="s">
+      <c r="J9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K9" s="24">
+      <c r="K9" s="22">
         <f t="shared" ref="K9:K10" si="10">1/3</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="L9" s="24">
+      <c r="L9" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M9" s="24">
+      <c r="M9" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N9" s="24">
+      <c r="N9" s="22">
         <f t="shared" si="2"/>
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="O9" s="24">
-        <v>100</v>
-      </c>
-      <c r="P9" s="25">
+      <c r="O9" s="22">
+        <v>0</v>
+      </c>
+      <c r="P9" s="23">
         <f t="shared" si="3"/>
-        <v>1.3888888888888888</v>
-      </c>
-      <c r="Q9" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R9" s="27">
+      <c r="R9" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S9" s="24">
+        <v>0</v>
+      </c>
+      <c r="S9" s="22">
         <f t="shared" ref="S9:S13" si="11">4/8</f>
         <v>0.5</v>
       </c>
-      <c r="T9" s="24">
+      <c r="T9" s="22">
         <f t="shared" si="7"/>
         <v>1.7241379310344827E-2</v>
       </c>
-      <c r="U9" s="29">
+      <c r="U9" s="27">
         <f t="shared" si="8"/>
-        <v>1.7241379310344827</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2"/>
     </row>
     <row r="10" spans="1:22" ht="88.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19">
+      <c r="A10" s="17">
         <v>2</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="C10" s="31">
-        <v>45659</v>
-      </c>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="30" t="s">
+        <v>306</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="K10" s="24">
+      <c r="K10" s="22">
         <f t="shared" si="10"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="L10" s="24">
+      <c r="L10" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M10" s="24">
+      <c r="M10" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N10" s="24">
+      <c r="N10" s="22">
         <f t="shared" si="2"/>
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="O10" s="24">
-        <v>100</v>
-      </c>
-      <c r="P10" s="25">
+      <c r="O10" s="22">
+        <v>0</v>
+      </c>
+      <c r="P10" s="23">
         <f t="shared" si="3"/>
-        <v>1.3888888888888888</v>
-      </c>
-      <c r="Q10" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R10" s="27">
+      <c r="R10" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S10" s="24">
+        <v>0</v>
+      </c>
+      <c r="S10" s="22">
         <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
-      <c r="T10" s="24">
+      <c r="T10" s="22">
         <f t="shared" si="7"/>
         <v>1.7241379310344827E-2</v>
       </c>
-      <c r="U10" s="29">
+      <c r="U10" s="27">
         <f t="shared" si="8"/>
-        <v>1.7241379310344827</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2"/>
     </row>
     <row r="11" spans="1:22" ht="51" x14ac:dyDescent="0.2">
-      <c r="A11" s="19">
+      <c r="A11" s="17">
         <v>2</v>
       </c>
-      <c r="B11" s="34" t="s">
+      <c r="B11" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="C11" s="32">
-        <v>45690</v>
-      </c>
-      <c r="D11" s="10" t="s">
+      <c r="C11" s="30" t="s">
+        <v>307</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="J11" s="10" t="s">
+      <c r="J11" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K11" s="24">
+      <c r="K11" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L11" s="24">
+      <c r="L11" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M11" s="24">
+      <c r="M11" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N11" s="24">
+      <c r="N11" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O11" s="24">
-        <v>100</v>
-      </c>
-      <c r="P11" s="25">
+      <c r="O11" s="22">
+        <v>2</v>
+      </c>
+      <c r="P11" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q11" s="24">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="Q11" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R11" s="27">
+      <c r="R11" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S11" s="24">
+        <v>3.9215686274509803E-2</v>
+      </c>
+      <c r="S11" s="22">
         <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
-      <c r="T11" s="24">
+      <c r="T11" s="22">
         <f t="shared" si="7"/>
         <v>1.7241379310344827E-2</v>
       </c>
-      <c r="U11" s="29">
+      <c r="U11" s="27">
         <f t="shared" si="8"/>
-        <v>1.7241379310344827</v>
+        <v>3.4482758620689655E-2</v>
       </c>
       <c r="V11" s="2"/>
     </row>
     <row r="12" spans="1:22" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="19">
+      <c r="A12" s="17">
         <v>2</v>
       </c>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="C12" s="32">
-        <v>45690</v>
-      </c>
-      <c r="D12" s="10" t="s">
+      <c r="C12" s="30" t="s">
+        <v>307</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I12" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="K12" s="24">
+      <c r="K12" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L12" s="24">
+      <c r="L12" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M12" s="24">
+      <c r="M12" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N12" s="24">
+      <c r="N12" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O12" s="24">
-        <v>100</v>
-      </c>
-      <c r="P12" s="25">
+      <c r="O12" s="22">
+        <v>4</v>
+      </c>
+      <c r="P12" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q12" s="24">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="Q12" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R12" s="27">
+      <c r="R12" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S12" s="24">
+        <v>7.8431372549019607E-2</v>
+      </c>
+      <c r="S12" s="22">
         <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
-      <c r="T12" s="24">
+      <c r="T12" s="22">
         <f t="shared" si="7"/>
         <v>1.7241379310344827E-2</v>
       </c>
-      <c r="U12" s="29">
+      <c r="U12" s="27">
         <f t="shared" si="8"/>
-        <v>1.7241379310344827</v>
+        <v>6.8965517241379309E-2</v>
       </c>
       <c r="V12" s="2"/>
     </row>
     <row r="13" spans="1:22" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A13" s="19">
+      <c r="A13" s="17">
         <v>2</v>
       </c>
-      <c r="B13" s="34" t="s">
+      <c r="B13" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="C13" s="12">
-        <v>45718</v>
-      </c>
-      <c r="D13" s="10" t="s">
+      <c r="C13" s="30" t="s">
+        <v>308</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="J13" s="10" t="s">
+      <c r="J13" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="24">
+      <c r="K13" s="22">
         <v>1</v>
       </c>
-      <c r="L13" s="24">
+      <c r="L13" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M13" s="24">
+      <c r="M13" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N13" s="24">
+      <c r="N13" s="22">
         <f t="shared" si="2"/>
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="O13" s="24">
-        <v>100</v>
-      </c>
-      <c r="P13" s="25">
+      <c r="O13" s="22">
+        <v>6</v>
+      </c>
+      <c r="P13" s="23">
         <f t="shared" si="3"/>
-        <v>4.1666666666666661</v>
-      </c>
-      <c r="Q13" s="24">
+        <v>0.25</v>
+      </c>
+      <c r="Q13" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R13" s="27">
+      <c r="R13" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S13" s="24">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="S13" s="22">
         <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
-      <c r="T13" s="24">
+      <c r="T13" s="22">
         <f t="shared" si="7"/>
         <v>1.7241379310344827E-2</v>
       </c>
-      <c r="U13" s="29">
+      <c r="U13" s="27">
         <f t="shared" si="8"/>
-        <v>1.7241379310344827</v>
+        <v>0.10344827586206896</v>
       </c>
       <c r="V13" s="2"/>
     </row>
     <row r="14" spans="1:22" ht="102" x14ac:dyDescent="0.2">
-      <c r="A14" s="19">
+      <c r="A14" s="17">
         <v>3</v>
       </c>
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="C14" s="31">
-        <v>45660</v>
-      </c>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="30" t="s">
+        <v>309</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="H14" s="13" t="s">
+      <c r="H14" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J14" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="K14" s="24">
+      <c r="K14" s="22">
         <f>1/3</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="L14" s="24">
+      <c r="L14" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M14" s="24">
+      <c r="M14" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N14" s="24">
+      <c r="N14" s="22">
         <f t="shared" si="2"/>
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="O14" s="24">
-        <v>100</v>
-      </c>
-      <c r="P14" s="25">
+      <c r="O14" s="22">
+        <v>8</v>
+      </c>
+      <c r="P14" s="23">
         <f t="shared" si="3"/>
-        <v>1.3888888888888888</v>
-      </c>
-      <c r="Q14" s="24">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="Q14" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R14" s="27">
+      <c r="R14" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S14" s="24">
+        <v>0.15686274509803921</v>
+      </c>
+      <c r="S14" s="22">
         <f>1/8</f>
         <v>0.125</v>
       </c>
-      <c r="T14" s="24">
+      <c r="T14" s="22">
         <f t="shared" si="7"/>
         <v>4.3103448275862068E-3</v>
       </c>
-      <c r="U14" s="29">
+      <c r="U14" s="27">
         <f t="shared" si="8"/>
-        <v>0.43103448275862066</v>
+        <v>3.4482758620689655E-2</v>
       </c>
       <c r="V14" s="2"/>
     </row>
     <row r="15" spans="1:22" ht="102" x14ac:dyDescent="0.2">
-      <c r="A15" s="19">
+      <c r="A15" s="17">
         <v>3</v>
       </c>
-      <c r="B15" s="34" t="s">
+      <c r="B15" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="C15" s="31">
-        <v>45660</v>
-      </c>
-      <c r="D15" s="7" t="s">
+      <c r="C15" s="30" t="s">
+        <v>309</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="I15" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="K15" s="24">
+      <c r="K15" s="22">
         <f t="shared" ref="K15:K16" si="12">1/3</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="L15" s="24">
+      <c r="L15" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M15" s="24">
+      <c r="M15" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N15" s="24">
+      <c r="N15" s="22">
         <f t="shared" si="2"/>
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="O15" s="24">
-        <v>100</v>
-      </c>
-      <c r="P15" s="25">
+      <c r="O15" s="22">
+        <v>10</v>
+      </c>
+      <c r="P15" s="23">
         <f t="shared" si="3"/>
-        <v>1.3888888888888888</v>
-      </c>
-      <c r="Q15" s="24">
+        <v>0.1388888888888889</v>
+      </c>
+      <c r="Q15" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R15" s="27">
+      <c r="R15" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S15" s="24">
+        <v>0.19607843137254902</v>
+      </c>
+      <c r="S15" s="22">
         <f t="shared" ref="S15:S20" si="13">1/8</f>
         <v>0.125</v>
       </c>
-      <c r="T15" s="24">
+      <c r="T15" s="22">
         <f t="shared" si="7"/>
         <v>4.3103448275862068E-3</v>
       </c>
-      <c r="U15" s="29">
+      <c r="U15" s="27">
         <f t="shared" si="8"/>
-        <v>0.43103448275862066</v>
+        <v>4.3103448275862072E-2</v>
       </c>
       <c r="V15" s="2"/>
     </row>
     <row r="16" spans="1:22" ht="100.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19">
+      <c r="A16" s="17">
         <v>3</v>
       </c>
-      <c r="B16" s="34" t="s">
+      <c r="B16" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="C16" s="31">
-        <v>45660</v>
-      </c>
-      <c r="D16" s="7" t="s">
+      <c r="C16" s="30" t="s">
+        <v>309</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="J16" s="13" t="s">
+      <c r="J16" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="K16" s="24">
+      <c r="K16" s="22">
         <f t="shared" si="12"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="L16" s="24">
+      <c r="L16" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M16" s="24">
+      <c r="M16" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N16" s="24">
+      <c r="N16" s="22">
         <f t="shared" si="2"/>
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="O16" s="24">
-        <v>100</v>
-      </c>
-      <c r="P16" s="25">
+      <c r="O16" s="22">
+        <v>12</v>
+      </c>
+      <c r="P16" s="23">
         <f t="shared" si="3"/>
-        <v>1.3888888888888888</v>
-      </c>
-      <c r="Q16" s="24">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="Q16" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R16" s="27">
+      <c r="R16" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S16" s="24">
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="S16" s="22">
         <f t="shared" si="13"/>
         <v>0.125</v>
       </c>
-      <c r="T16" s="24">
+      <c r="T16" s="22">
         <f t="shared" si="7"/>
         <v>4.3103448275862068E-3</v>
       </c>
-      <c r="U16" s="29">
+      <c r="U16" s="27">
         <f t="shared" si="8"/>
-        <v>0.43103448275862066</v>
+        <v>5.1724137931034482E-2</v>
       </c>
       <c r="V16" s="2"/>
     </row>
     <row r="17" spans="1:22" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="19">
+      <c r="A17" s="17">
         <v>3</v>
       </c>
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="C17" s="32">
-        <v>45691</v>
-      </c>
-      <c r="D17" s="10" t="s">
+      <c r="C17" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="I17" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="J17" s="14" t="s">
+      <c r="J17" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="K17" s="24">
+      <c r="K17" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L17" s="24">
+      <c r="L17" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M17" s="24">
+      <c r="M17" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N17" s="24">
+      <c r="N17" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O17" s="24">
-        <v>100</v>
-      </c>
-      <c r="P17" s="25">
+      <c r="O17" s="22">
+        <v>14</v>
+      </c>
+      <c r="P17" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q17" s="24">
+        <v>0.29166666666666663</v>
+      </c>
+      <c r="Q17" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R17" s="27">
+      <c r="R17" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S17" s="24">
+        <v>0.27450980392156865</v>
+      </c>
+      <c r="S17" s="22">
         <f t="shared" si="13"/>
         <v>0.125</v>
       </c>
-      <c r="T17" s="24">
+      <c r="T17" s="22">
         <f t="shared" si="7"/>
         <v>4.3103448275862068E-3</v>
       </c>
-      <c r="U17" s="29">
+      <c r="U17" s="27">
         <f t="shared" si="8"/>
-        <v>0.43103448275862066</v>
+        <v>6.0344827586206892E-2</v>
       </c>
       <c r="V17" s="2"/>
     </row>
     <row r="18" spans="1:22" ht="114.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="19">
+      <c r="A18" s="17">
         <v>3</v>
       </c>
-      <c r="B18" s="34" t="s">
+      <c r="B18" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="C18" s="32">
-        <v>45691</v>
-      </c>
-      <c r="D18" s="10" t="s">
+      <c r="C18" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="J18" s="13" t="s">
+      <c r="J18" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="K18" s="24">
+      <c r="K18" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L18" s="24">
+      <c r="L18" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M18" s="24">
+      <c r="M18" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N18" s="24">
+      <c r="N18" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O18" s="24">
-        <v>100</v>
-      </c>
-      <c r="P18" s="25">
+      <c r="O18" s="22">
+        <v>16</v>
+      </c>
+      <c r="P18" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q18" s="24">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Q18" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R18" s="27">
+      <c r="R18" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S18" s="24">
+        <v>0.31372549019607843</v>
+      </c>
+      <c r="S18" s="22">
         <f t="shared" si="13"/>
         <v>0.125</v>
       </c>
-      <c r="T18" s="24">
+      <c r="T18" s="22">
         <f t="shared" si="7"/>
         <v>4.3103448275862068E-3</v>
       </c>
-      <c r="U18" s="29">
+      <c r="U18" s="27">
         <f t="shared" si="8"/>
-        <v>0.43103448275862066</v>
+        <v>6.8965517241379309E-2</v>
       </c>
       <c r="V18" s="2"/>
     </row>
     <row r="19" spans="1:22" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A19" s="19">
+      <c r="A19" s="17">
         <v>3</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="C19" s="32">
-        <v>45719</v>
-      </c>
-      <c r="D19" s="10" t="s">
+      <c r="C19" s="30" t="s">
+        <v>311</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I19" s="10" t="s">
+      <c r="I19" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="J19" s="14" t="s">
+      <c r="J19" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="K19" s="24">
+      <c r="K19" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L19" s="24">
+      <c r="L19" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M19" s="24">
+      <c r="M19" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N19" s="24">
+      <c r="N19" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O19" s="24">
-        <v>100</v>
-      </c>
-      <c r="P19" s="25">
+      <c r="O19" s="22">
+        <v>18</v>
+      </c>
+      <c r="P19" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q19" s="24">
+        <v>0.375</v>
+      </c>
+      <c r="Q19" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R19" s="27">
+      <c r="R19" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S19" s="24">
+        <v>0.3529411764705882</v>
+      </c>
+      <c r="S19" s="22">
         <f t="shared" si="13"/>
         <v>0.125</v>
       </c>
-      <c r="T19" s="24">
+      <c r="T19" s="22">
         <f t="shared" si="7"/>
         <v>4.3103448275862068E-3</v>
       </c>
-      <c r="U19" s="29">
+      <c r="U19" s="27">
         <f t="shared" si="8"/>
-        <v>0.43103448275862066</v>
+        <v>7.7586206896551727E-2</v>
       </c>
       <c r="V19" s="2"/>
     </row>
     <row r="20" spans="1:22" ht="102" x14ac:dyDescent="0.2">
-      <c r="A20" s="19">
+      <c r="A20" s="17">
         <v>3</v>
       </c>
-      <c r="B20" s="34" t="s">
+      <c r="B20" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="C20" s="32">
-        <v>45719</v>
-      </c>
-      <c r="D20" s="10" t="s">
+      <c r="C20" s="30" t="s">
+        <v>311</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="I20" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="J20" s="13" t="s">
+      <c r="J20" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="K20" s="24">
+      <c r="K20" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L20" s="24">
+      <c r="L20" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M20" s="24">
+      <c r="M20" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N20" s="24">
+      <c r="N20" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O20" s="24">
-        <v>100</v>
-      </c>
-      <c r="P20" s="25">
+      <c r="O20" s="22">
+        <v>20</v>
+      </c>
+      <c r="P20" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q20" s="24">
+        <v>0.41666666666666663</v>
+      </c>
+      <c r="Q20" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R20" s="27">
+      <c r="R20" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S20" s="24">
+        <v>0.39215686274509803</v>
+      </c>
+      <c r="S20" s="22">
         <f t="shared" si="13"/>
         <v>0.125</v>
       </c>
-      <c r="T20" s="24">
+      <c r="T20" s="22">
         <f t="shared" si="7"/>
         <v>4.3103448275862068E-3</v>
       </c>
-      <c r="U20" s="29">
+      <c r="U20" s="27">
         <f t="shared" si="8"/>
-        <v>0.43103448275862066</v>
+        <v>8.6206896551724144E-2</v>
       </c>
       <c r="V20" s="2"/>
     </row>
     <row r="21" spans="1:22" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A21" s="19">
+      <c r="A21" s="17">
         <v>4</v>
       </c>
-      <c r="B21" s="34" t="s">
+      <c r="B21" s="29" t="s">
         <v>298</v>
       </c>
-      <c r="C21" s="32">
-        <v>45661</v>
-      </c>
-      <c r="D21" s="10" t="s">
+      <c r="C21" s="30" t="s">
+        <v>312</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="G21" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="I21" s="10" t="s">
+      <c r="I21" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="J21" s="14" t="s">
+      <c r="J21" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="K21" s="24">
+      <c r="K21" s="22">
         <f>1/3</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="L21" s="24">
+      <c r="L21" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M21" s="24">
+      <c r="M21" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N21" s="24">
+      <c r="N21" s="22">
         <f t="shared" si="2"/>
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="O21" s="24">
-        <v>100</v>
-      </c>
-      <c r="P21" s="25">
+      <c r="O21" s="22">
+        <v>22</v>
+      </c>
+      <c r="P21" s="23">
         <f t="shared" si="3"/>
-        <v>1.3888888888888888</v>
-      </c>
-      <c r="Q21" s="24">
+        <v>0.30555555555555552</v>
+      </c>
+      <c r="Q21" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R21" s="27">
+      <c r="R21" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S21" s="24">
+        <v>0.43137254901960786</v>
+      </c>
+      <c r="S21" s="22">
         <v>1</v>
       </c>
-      <c r="T21" s="24">
+      <c r="T21" s="22">
         <f t="shared" si="7"/>
         <v>3.4482758620689655E-2</v>
       </c>
-      <c r="U21" s="29">
+      <c r="U21" s="27">
         <f t="shared" si="8"/>
-        <v>3.4482758620689653</v>
+        <v>0.75862068965517238</v>
       </c>
       <c r="V21" s="2"/>
     </row>
     <row r="22" spans="1:22" ht="102" x14ac:dyDescent="0.2">
-      <c r="A22" s="19">
+      <c r="A22" s="17">
         <v>4</v>
       </c>
-      <c r="B22" s="34" t="s">
+      <c r="B22" s="29" t="s">
         <v>298</v>
       </c>
-      <c r="C22" s="32">
-        <v>45661</v>
-      </c>
-      <c r="D22" s="10" t="s">
+      <c r="C22" s="30" t="s">
+        <v>312</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="G22" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H22" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="I22" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="J22" s="13" t="s">
+      <c r="J22" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="K22" s="24">
+      <c r="K22" s="22">
         <f t="shared" ref="K22:K23" si="14">1/3</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="L22" s="24">
+      <c r="L22" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M22" s="24">
+      <c r="M22" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N22" s="24">
+      <c r="N22" s="22">
         <f t="shared" si="2"/>
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="O22" s="24">
-        <v>100</v>
-      </c>
-      <c r="P22" s="25">
+      <c r="O22" s="22">
+        <v>0</v>
+      </c>
+      <c r="P22" s="23">
         <f t="shared" si="3"/>
-        <v>1.3888888888888888</v>
-      </c>
-      <c r="Q22" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R22" s="27">
+      <c r="R22" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S22" s="24">
+        <v>0</v>
+      </c>
+      <c r="S22" s="22">
         <v>1</v>
       </c>
-      <c r="T22" s="24">
+      <c r="T22" s="22">
         <f t="shared" si="7"/>
         <v>3.4482758620689655E-2</v>
       </c>
-      <c r="U22" s="29">
+      <c r="U22" s="27">
         <f t="shared" si="8"/>
-        <v>3.4482758620689653</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2"/>
     </row>
     <row r="23" spans="1:22" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="19">
+      <c r="A23" s="17">
         <v>4</v>
       </c>
-      <c r="B23" s="34" t="s">
+      <c r="B23" s="29" t="s">
         <v>298</v>
       </c>
-      <c r="C23" s="32">
-        <v>45661</v>
-      </c>
-      <c r="D23" s="10" t="s">
+      <c r="C23" s="30" t="s">
+        <v>312</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="G23" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="I23" s="10" t="s">
+      <c r="I23" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="J23" s="14" t="s">
+      <c r="J23" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="K23" s="24">
+      <c r="K23" s="22">
         <f t="shared" si="14"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="L23" s="24">
+      <c r="L23" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M23" s="24">
+      <c r="M23" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N23" s="24">
+      <c r="N23" s="22">
         <f t="shared" si="2"/>
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="O23" s="24">
-        <v>100</v>
-      </c>
-      <c r="P23" s="25">
+      <c r="O23" s="22">
+        <v>0</v>
+      </c>
+      <c r="P23" s="23">
         <f t="shared" si="3"/>
-        <v>1.3888888888888888</v>
-      </c>
-      <c r="Q23" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R23" s="27">
+      <c r="R23" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S23" s="24">
+        <v>0</v>
+      </c>
+      <c r="S23" s="22">
         <v>1</v>
       </c>
-      <c r="T23" s="24">
+      <c r="T23" s="22">
         <f t="shared" si="7"/>
         <v>3.4482758620689655E-2</v>
       </c>
-      <c r="U23" s="29">
+      <c r="U23" s="27">
         <f t="shared" si="8"/>
-        <v>3.4482758620689653</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2"/>
     </row>
     <row r="24" spans="1:22" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A24" s="19">
+      <c r="A24" s="17">
         <v>4</v>
       </c>
-      <c r="B24" s="34" t="s">
+      <c r="B24" s="29" t="s">
         <v>298</v>
       </c>
-      <c r="C24" s="33">
-        <v>45692</v>
-      </c>
-      <c r="D24" s="18" t="s">
+      <c r="C24" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="D24" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="G24" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="H24" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="I24" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="J24" s="13" t="s">
+      <c r="J24" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="K24" s="24">
+      <c r="K24" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L24" s="24">
+      <c r="L24" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M24" s="24">
+      <c r="M24" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N24" s="24">
+      <c r="N24" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O24" s="24">
-        <v>100</v>
-      </c>
-      <c r="P24" s="25">
+      <c r="O24" s="22">
+        <v>0</v>
+      </c>
+      <c r="P24" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q24" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R24" s="27">
+      <c r="R24" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S24" s="24">
+        <v>0</v>
+      </c>
+      <c r="S24" s="22">
         <v>1</v>
       </c>
-      <c r="T24" s="24">
+      <c r="T24" s="22">
         <f t="shared" si="7"/>
         <v>3.4482758620689655E-2</v>
       </c>
-      <c r="U24" s="29">
+      <c r="U24" s="27">
         <f t="shared" si="8"/>
-        <v>3.4482758620689653</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2"/>
     </row>
     <row r="25" spans="1:22" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A25" s="19">
+      <c r="A25" s="17">
         <v>4</v>
       </c>
-      <c r="B25" s="34" t="s">
+      <c r="B25" s="29" t="s">
         <v>298</v>
       </c>
-      <c r="C25" s="33">
-        <v>45692</v>
-      </c>
-      <c r="D25" s="18" t="s">
+      <c r="C25" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="D25" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="G25" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H25" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="I25" s="10" t="s">
+      <c r="I25" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="J25" s="14" t="s">
+      <c r="J25" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="K25" s="24">
+      <c r="K25" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L25" s="24">
+      <c r="L25" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M25" s="24">
+      <c r="M25" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N25" s="24">
+      <c r="N25" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O25" s="24">
-        <v>100</v>
-      </c>
-      <c r="P25" s="25">
+      <c r="O25" s="22">
+        <v>0</v>
+      </c>
+      <c r="P25" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q25" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R25" s="27">
+      <c r="R25" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S25" s="24">
+        <v>0</v>
+      </c>
+      <c r="S25" s="22">
         <v>1</v>
       </c>
-      <c r="T25" s="24">
+      <c r="T25" s="22">
         <f t="shared" si="7"/>
         <v>3.4482758620689655E-2</v>
       </c>
-      <c r="U25" s="29">
+      <c r="U25" s="27">
         <f t="shared" si="8"/>
-        <v>3.4482758620689653</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2"/>
     </row>
     <row r="26" spans="1:22" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A26" s="19">
+      <c r="A26" s="17">
         <v>4</v>
       </c>
-      <c r="B26" s="34" t="s">
+      <c r="B26" s="29" t="s">
         <v>298</v>
       </c>
-      <c r="C26" s="33">
-        <v>45720</v>
-      </c>
-      <c r="D26" s="18" t="s">
+      <c r="C26" s="30" t="s">
+        <v>314</v>
+      </c>
+      <c r="D26" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="H26" s="7" t="s">
+      <c r="H26" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="I26" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="J26" s="7" t="s">
+      <c r="J26" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K26" s="24">
+      <c r="K26" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L26" s="24">
+      <c r="L26" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M26" s="24">
+      <c r="M26" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N26" s="24">
+      <c r="N26" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O26" s="24">
-        <v>100</v>
-      </c>
-      <c r="P26" s="25">
+      <c r="O26" s="22">
+        <v>2</v>
+      </c>
+      <c r="P26" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q26" s="24">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="Q26" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R26" s="27">
+      <c r="R26" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S26" s="24">
+        <v>3.9215686274509803E-2</v>
+      </c>
+      <c r="S26" s="22">
         <v>1</v>
       </c>
-      <c r="T26" s="24">
+      <c r="T26" s="22">
         <f t="shared" si="7"/>
         <v>3.4482758620689655E-2</v>
       </c>
-      <c r="U26" s="29">
+      <c r="U26" s="27">
         <f t="shared" si="8"/>
-        <v>3.4482758620689653</v>
+        <v>6.8965517241379309E-2</v>
       </c>
       <c r="V26" s="2"/>
     </row>
     <row r="27" spans="1:22" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A27" s="19">
+      <c r="A27" s="17">
         <v>4</v>
       </c>
-      <c r="B27" s="34" t="s">
+      <c r="B27" s="29" t="s">
         <v>298</v>
       </c>
-      <c r="C27" s="33">
-        <v>45720</v>
-      </c>
-      <c r="D27" s="18" t="s">
+      <c r="C27" s="30" t="s">
+        <v>314</v>
+      </c>
+      <c r="D27" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="G27" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="I27" s="10" t="s">
+      <c r="I27" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="J27" s="10" t="s">
+      <c r="J27" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="K27" s="24">
+      <c r="K27" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L27" s="24">
+      <c r="L27" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M27" s="24">
+      <c r="M27" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N27" s="24">
+      <c r="N27" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O27" s="24">
-        <v>100</v>
-      </c>
-      <c r="P27" s="25">
+      <c r="O27" s="22">
+        <v>4</v>
+      </c>
+      <c r="P27" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q27" s="24">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="Q27" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R27" s="27">
+      <c r="R27" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S27" s="24">
+        <v>7.8431372549019607E-2</v>
+      </c>
+      <c r="S27" s="22">
         <v>1</v>
       </c>
-      <c r="T27" s="24">
+      <c r="T27" s="22">
         <f t="shared" si="7"/>
         <v>3.4482758620689655E-2</v>
       </c>
-      <c r="U27" s="29">
+      <c r="U27" s="27">
         <f t="shared" si="8"/>
-        <v>3.4482758620689653</v>
+        <v>0.13793103448275862</v>
       </c>
       <c r="V27" s="2"/>
     </row>
     <row r="28" spans="1:22" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="19">
+      <c r="A28" s="17">
         <v>5</v>
       </c>
-      <c r="B28" s="34" t="s">
+      <c r="B28" s="29" t="s">
         <v>299</v>
       </c>
-      <c r="C28" s="31">
-        <v>45662</v>
-      </c>
-      <c r="D28" s="7" t="s">
+      <c r="C28" s="30" t="s">
+        <v>315</v>
+      </c>
+      <c r="D28" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="G28" s="7" t="s">
+      <c r="G28" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="H28" s="7" t="s">
+      <c r="H28" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="I28" s="7" t="s">
+      <c r="I28" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="J28" s="7" t="s">
+      <c r="J28" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="K28" s="24">
+      <c r="K28" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L28" s="24">
+      <c r="L28" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M28" s="24">
+      <c r="M28" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N28" s="24">
+      <c r="N28" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O28" s="24">
-        <v>100</v>
-      </c>
-      <c r="P28" s="25">
+      <c r="O28" s="22">
+        <v>6</v>
+      </c>
+      <c r="P28" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q28" s="24">
+        <v>0.125</v>
+      </c>
+      <c r="Q28" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R28" s="27">
+      <c r="R28" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S28" s="24">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="S28" s="22">
         <f>5/8</f>
         <v>0.625</v>
       </c>
-      <c r="T28" s="24">
+      <c r="T28" s="22">
         <f t="shared" si="7"/>
         <v>2.1551724137931036E-2</v>
       </c>
-      <c r="U28" s="29">
+      <c r="U28" s="27">
         <f t="shared" si="8"/>
-        <v>2.1551724137931036</v>
+        <v>0.12931034482758622</v>
       </c>
       <c r="V28" s="2"/>
     </row>
     <row r="29" spans="1:22" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A29" s="19">
+      <c r="A29" s="17">
         <v>5</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="29" t="s">
         <v>299</v>
       </c>
-      <c r="C29" s="31">
-        <v>45662</v>
-      </c>
-      <c r="D29" s="7" t="s">
+      <c r="C29" s="30" t="s">
+        <v>315</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="F29" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="G29" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="H29" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="I29" s="10" t="s">
+      <c r="I29" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="J29" s="10" t="s">
+      <c r="J29" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="K29" s="24">
+      <c r="K29" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L29" s="24">
+      <c r="L29" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M29" s="24">
+      <c r="M29" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N29" s="24">
+      <c r="N29" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O29" s="24">
-        <v>100</v>
-      </c>
-      <c r="P29" s="25">
+      <c r="O29" s="22">
+        <v>8</v>
+      </c>
+      <c r="P29" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q29" s="24">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="Q29" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R29" s="27">
+      <c r="R29" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S29" s="24">
+        <v>0.15686274509803921</v>
+      </c>
+      <c r="S29" s="22">
         <f t="shared" ref="S29:S33" si="15">5/8</f>
         <v>0.625</v>
       </c>
-      <c r="T29" s="24">
+      <c r="T29" s="22">
         <f t="shared" si="7"/>
         <v>2.1551724137931036E-2</v>
       </c>
-      <c r="U29" s="29">
+      <c r="U29" s="27">
         <f t="shared" si="8"/>
-        <v>2.1551724137931036</v>
+        <v>0.17241379310344829</v>
       </c>
       <c r="V29" s="2"/>
     </row>
     <row r="30" spans="1:22" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A30" s="19">
+      <c r="A30" s="17">
         <v>5</v>
       </c>
-      <c r="B30" s="34" t="s">
+      <c r="B30" s="29" t="s">
         <v>299</v>
       </c>
-      <c r="C30" s="31">
-        <v>45693</v>
-      </c>
-      <c r="D30" s="7" t="s">
+      <c r="C30" s="30" t="s">
+        <v>316</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="G30" s="7" t="s">
+      <c r="G30" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="H30" s="7" t="s">
+      <c r="H30" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="I30" s="7" t="s">
+      <c r="I30" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="J30" s="7" t="s">
+      <c r="J30" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="K30" s="24">
+      <c r="K30" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L30" s="24">
+      <c r="L30" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M30" s="24">
+      <c r="M30" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N30" s="24">
+      <c r="N30" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O30" s="24">
-        <v>100</v>
-      </c>
-      <c r="P30" s="25">
+      <c r="O30" s="22">
+        <v>10</v>
+      </c>
+      <c r="P30" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q30" s="24">
+        <v>0.20833333333333331</v>
+      </c>
+      <c r="Q30" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R30" s="27">
+      <c r="R30" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S30" s="24">
+        <v>0.19607843137254902</v>
+      </c>
+      <c r="S30" s="22">
         <f t="shared" si="15"/>
         <v>0.625</v>
       </c>
-      <c r="T30" s="24">
+      <c r="T30" s="22">
         <f t="shared" si="7"/>
         <v>2.1551724137931036E-2</v>
       </c>
-      <c r="U30" s="29">
+      <c r="U30" s="27">
         <f t="shared" si="8"/>
-        <v>2.1551724137931036</v>
+        <v>0.21551724137931036</v>
       </c>
       <c r="V30" s="2"/>
     </row>
     <row r="31" spans="1:22" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A31" s="19">
+      <c r="A31" s="17">
         <v>5</v>
       </c>
-      <c r="B31" s="34" t="s">
+      <c r="B31" s="29" t="s">
         <v>299</v>
       </c>
-      <c r="C31" s="31">
-        <v>45693</v>
-      </c>
-      <c r="D31" s="7" t="s">
+      <c r="C31" s="30" t="s">
+        <v>316</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="G31" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H31" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="I31" s="10" t="s">
+      <c r="I31" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="J31" s="10" t="s">
+      <c r="J31" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K31" s="24">
+      <c r="K31" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L31" s="24">
+      <c r="L31" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M31" s="24">
+      <c r="M31" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N31" s="24">
+      <c r="N31" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O31" s="24">
-        <v>100</v>
-      </c>
-      <c r="P31" s="25">
+      <c r="O31" s="22">
+        <v>12</v>
+      </c>
+      <c r="P31" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q31" s="24">
+        <v>0.25</v>
+      </c>
+      <c r="Q31" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R31" s="27">
+      <c r="R31" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S31" s="24">
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="S31" s="22">
         <f t="shared" si="15"/>
         <v>0.625</v>
       </c>
-      <c r="T31" s="24">
+      <c r="T31" s="22">
         <f t="shared" si="7"/>
         <v>2.1551724137931036E-2</v>
       </c>
-      <c r="U31" s="29">
+      <c r="U31" s="27">
         <f t="shared" si="8"/>
-        <v>2.1551724137931036</v>
+        <v>0.25862068965517243</v>
       </c>
       <c r="V31" s="2"/>
     </row>
     <row r="32" spans="1:22" ht="51" x14ac:dyDescent="0.2">
-      <c r="A32" s="19">
+      <c r="A32" s="17">
         <v>5</v>
       </c>
-      <c r="B32" s="34" t="s">
+      <c r="B32" s="29" t="s">
         <v>299</v>
       </c>
-      <c r="C32" s="31">
-        <v>45721</v>
-      </c>
-      <c r="D32" s="7" t="s">
+      <c r="C32" s="30" t="s">
+        <v>317</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E32" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="G32" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="H32" s="7" t="s">
+      <c r="H32" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="I32" s="7" t="s">
+      <c r="I32" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="J32" s="7" t="s">
+      <c r="J32" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K32" s="24">
+      <c r="K32" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L32" s="24">
+      <c r="L32" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M32" s="24">
+      <c r="M32" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N32" s="24">
+      <c r="N32" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O32" s="24">
-        <v>100</v>
-      </c>
-      <c r="P32" s="25">
+      <c r="O32" s="22">
+        <v>14</v>
+      </c>
+      <c r="P32" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q32" s="24">
+        <v>0.29166666666666663</v>
+      </c>
+      <c r="Q32" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R32" s="27">
+      <c r="R32" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S32" s="24">
+        <v>0.27450980392156865</v>
+      </c>
+      <c r="S32" s="22">
         <f t="shared" si="15"/>
         <v>0.625</v>
       </c>
-      <c r="T32" s="24">
+      <c r="T32" s="22">
         <f t="shared" si="7"/>
         <v>2.1551724137931036E-2</v>
       </c>
-      <c r="U32" s="29">
+      <c r="U32" s="27">
         <f t="shared" si="8"/>
-        <v>2.1551724137931036</v>
+        <v>0.30172413793103448</v>
       </c>
       <c r="V32" s="2"/>
     </row>
     <row r="33" spans="1:22" ht="51" x14ac:dyDescent="0.2">
-      <c r="A33" s="19">
+      <c r="A33" s="17">
         <v>5</v>
       </c>
-      <c r="B33" s="34" t="s">
+      <c r="B33" s="29" t="s">
         <v>299</v>
       </c>
-      <c r="C33" s="31">
-        <v>45721</v>
-      </c>
-      <c r="D33" s="7" t="s">
+      <c r="C33" s="30" t="s">
+        <v>317</v>
+      </c>
+      <c r="D33" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="F33" s="10" t="s">
+      <c r="F33" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="G33" s="10" t="s">
+      <c r="G33" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H33" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="I33" s="10" t="s">
+      <c r="I33" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="J33" s="10" t="s">
+      <c r="J33" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K33" s="24">
+      <c r="K33" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L33" s="24">
+      <c r="L33" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M33" s="24">
+      <c r="M33" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N33" s="24">
+      <c r="N33" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O33" s="24">
-        <v>100</v>
-      </c>
-      <c r="P33" s="25">
+      <c r="O33" s="22">
+        <v>16</v>
+      </c>
+      <c r="P33" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q33" s="24">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Q33" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R33" s="27">
+      <c r="R33" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S33" s="24">
+        <v>0.31372549019607843</v>
+      </c>
+      <c r="S33" s="22">
         <f t="shared" si="15"/>
         <v>0.625</v>
       </c>
-      <c r="T33" s="24">
+      <c r="T33" s="22">
         <f t="shared" si="7"/>
         <v>2.1551724137931036E-2</v>
       </c>
-      <c r="U33" s="29">
+      <c r="U33" s="27">
         <f t="shared" si="8"/>
-        <v>2.1551724137931036</v>
+        <v>0.34482758620689657</v>
       </c>
       <c r="V33" s="2"/>
     </row>
     <row r="34" spans="1:22" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A34" s="19">
+      <c r="A34" s="17">
         <v>6</v>
       </c>
-      <c r="B34" s="34" t="s">
+      <c r="B34" s="29" t="s">
         <v>300</v>
       </c>
-      <c r="C34" s="31">
-        <v>45663</v>
-      </c>
-      <c r="D34" s="7" t="s">
+      <c r="C34" s="30" t="s">
+        <v>318</v>
+      </c>
+      <c r="D34" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="G34" s="7" t="s">
+      <c r="G34" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="H34" s="7" t="s">
+      <c r="H34" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="I34" s="7" t="s">
+      <c r="I34" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="J34" s="7" t="s">
+      <c r="J34" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K34" s="24">
+      <c r="K34" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L34" s="24">
+      <c r="L34" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M34" s="24">
+      <c r="M34" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N34" s="24">
+      <c r="N34" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O34" s="24">
-        <v>100</v>
-      </c>
-      <c r="P34" s="25">
+      <c r="O34" s="22">
+        <v>18</v>
+      </c>
+      <c r="P34" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q34" s="24">
+        <v>0.375</v>
+      </c>
+      <c r="Q34" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R34" s="27">
+      <c r="R34" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S34" s="24">
+        <v>0.3529411764705882</v>
+      </c>
+      <c r="S34" s="22">
         <f>6/8</f>
         <v>0.75</v>
       </c>
-      <c r="T34" s="24">
+      <c r="T34" s="22">
         <f t="shared" si="7"/>
         <v>2.5862068965517241E-2</v>
       </c>
-      <c r="U34" s="29">
+      <c r="U34" s="27">
         <f t="shared" si="8"/>
-        <v>2.5862068965517242</v>
+        <v>0.46551724137931033</v>
       </c>
       <c r="V34" s="2"/>
     </row>
     <row r="35" spans="1:22" ht="51" x14ac:dyDescent="0.2">
-      <c r="A35" s="19">
+      <c r="A35" s="17">
         <v>6</v>
       </c>
-      <c r="B35" s="34" t="s">
+      <c r="B35" s="29" t="s">
         <v>300</v>
       </c>
-      <c r="C35" s="31">
-        <v>45663</v>
-      </c>
-      <c r="D35" s="7" t="s">
+      <c r="C35" s="30" t="s">
+        <v>318</v>
+      </c>
+      <c r="D35" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="F35" s="10" t="s">
+      <c r="F35" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="G35" s="10" t="s">
+      <c r="G35" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="H35" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="I35" s="10" t="s">
+      <c r="I35" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="J35" s="10" t="s">
+      <c r="J35" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K35" s="24">
+      <c r="K35" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L35" s="24">
+      <c r="L35" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M35" s="24">
+      <c r="M35" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N35" s="24">
+      <c r="N35" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O35" s="24">
-        <v>100</v>
-      </c>
-      <c r="P35" s="25">
+      <c r="O35" s="22">
+        <v>20</v>
+      </c>
+      <c r="P35" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q35" s="24">
+        <v>0.41666666666666663</v>
+      </c>
+      <c r="Q35" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R35" s="27">
+      <c r="R35" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S35" s="24">
+        <v>0.39215686274509803</v>
+      </c>
+      <c r="S35" s="22">
         <f t="shared" ref="S35:S40" si="16">6/8</f>
         <v>0.75</v>
       </c>
-      <c r="T35" s="24">
+      <c r="T35" s="22">
         <f t="shared" si="7"/>
         <v>2.5862068965517241E-2</v>
       </c>
-      <c r="U35" s="29">
+      <c r="U35" s="27">
         <f t="shared" si="8"/>
-        <v>2.5862068965517242</v>
+        <v>0.51724137931034486</v>
       </c>
       <c r="V35" s="2"/>
     </row>
     <row r="36" spans="1:22" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A36" s="19">
+      <c r="A36" s="17">
         <v>6</v>
       </c>
-      <c r="B36" s="34" t="s">
+      <c r="B36" s="29" t="s">
         <v>300</v>
       </c>
-      <c r="C36" s="31">
-        <v>45694</v>
-      </c>
-      <c r="D36" s="7" t="s">
+      <c r="C36" s="30" t="s">
+        <v>319</v>
+      </c>
+      <c r="D36" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="E36" s="16" t="s">
+      <c r="E36" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="F36" s="13" t="s">
+      <c r="F36" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="G36" s="13" t="s">
+      <c r="G36" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="H36" s="7" t="s">
+      <c r="H36" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="I36" s="7" t="s">
+      <c r="I36" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="J36" s="7" t="s">
+      <c r="J36" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K36" s="24">
+      <c r="K36" s="22">
         <f>1/3</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="L36" s="24">
+      <c r="L36" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M36" s="24">
+      <c r="M36" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N36" s="24">
+      <c r="N36" s="22">
         <f t="shared" si="2"/>
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="O36" s="24">
-        <v>100</v>
-      </c>
-      <c r="P36" s="25">
+      <c r="O36" s="22">
+        <v>0</v>
+      </c>
+      <c r="P36" s="23">
         <f t="shared" si="3"/>
-        <v>1.3888888888888888</v>
-      </c>
-      <c r="Q36" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R36" s="27">
+      <c r="R36" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S36" s="24">
+        <v>0</v>
+      </c>
+      <c r="S36" s="22">
         <f t="shared" si="16"/>
         <v>0.75</v>
       </c>
-      <c r="T36" s="24">
+      <c r="T36" s="22">
         <f t="shared" si="7"/>
         <v>2.5862068965517241E-2</v>
       </c>
-      <c r="U36" s="29">
+      <c r="U36" s="27">
         <f t="shared" si="8"/>
-        <v>2.5862068965517242</v>
+        <v>0</v>
       </c>
       <c r="V36" s="2"/>
     </row>
     <row r="37" spans="1:22" ht="51" x14ac:dyDescent="0.2">
-      <c r="A37" s="19">
+      <c r="A37" s="17">
         <v>6</v>
       </c>
-      <c r="B37" s="34" t="s">
+      <c r="B37" s="29" t="s">
         <v>300</v>
       </c>
-      <c r="C37" s="31">
-        <v>45694</v>
-      </c>
-      <c r="D37" s="7" t="s">
+      <c r="C37" s="30" t="s">
+        <v>319</v>
+      </c>
+      <c r="D37" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="E37" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="F37" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="G37" s="10" t="s">
+      <c r="G37" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="H37" s="10" t="s">
+      <c r="H37" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="I37" s="10" t="s">
+      <c r="I37" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="J37" s="10" t="s">
+      <c r="J37" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="K37" s="24">
+      <c r="K37" s="22">
         <f t="shared" ref="K37:K38" si="17">1/3</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="L37" s="24">
+      <c r="L37" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M37" s="24">
+      <c r="M37" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N37" s="24">
+      <c r="N37" s="22">
         <f t="shared" si="2"/>
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="O37" s="24">
-        <v>100</v>
-      </c>
-      <c r="P37" s="25">
+      <c r="O37" s="22">
+        <v>0</v>
+      </c>
+      <c r="P37" s="23">
         <f t="shared" si="3"/>
-        <v>1.3888888888888888</v>
-      </c>
-      <c r="Q37" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R37" s="27">
+      <c r="R37" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S37" s="24">
+        <v>0</v>
+      </c>
+      <c r="S37" s="22">
         <f t="shared" si="16"/>
         <v>0.75</v>
       </c>
-      <c r="T37" s="24">
+      <c r="T37" s="22">
         <f t="shared" si="7"/>
         <v>2.5862068965517241E-2</v>
       </c>
-      <c r="U37" s="29">
+      <c r="U37" s="27">
         <f t="shared" si="8"/>
-        <v>2.5862068965517242</v>
+        <v>0</v>
       </c>
       <c r="V37" s="2"/>
     </row>
     <row r="38" spans="1:22" ht="51" x14ac:dyDescent="0.2">
-      <c r="A38" s="19">
+      <c r="A38" s="17">
         <v>6</v>
       </c>
-      <c r="B38" s="34" t="s">
+      <c r="B38" s="29" t="s">
         <v>300</v>
       </c>
-      <c r="C38" s="31">
-        <v>45694</v>
-      </c>
-      <c r="D38" s="7" t="s">
+      <c r="C38" s="30" t="s">
+        <v>319</v>
+      </c>
+      <c r="D38" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="G38" s="7" t="s">
+      <c r="G38" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="H38" s="7" t="s">
+      <c r="H38" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="I38" s="7" t="s">
+      <c r="I38" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="J38" s="7" t="s">
+      <c r="J38" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K38" s="24">
+      <c r="K38" s="22">
         <f t="shared" si="17"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="L38" s="24">
+      <c r="L38" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M38" s="24">
+      <c r="M38" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N38" s="24">
+      <c r="N38" s="22">
         <f t="shared" si="2"/>
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="O38" s="24">
-        <v>100</v>
-      </c>
-      <c r="P38" s="25">
+      <c r="O38" s="22">
+        <v>0</v>
+      </c>
+      <c r="P38" s="23">
         <f t="shared" si="3"/>
-        <v>1.3888888888888888</v>
-      </c>
-      <c r="Q38" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R38" s="27">
+      <c r="R38" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S38" s="24">
+        <v>0</v>
+      </c>
+      <c r="S38" s="22">
         <f t="shared" si="16"/>
         <v>0.75</v>
       </c>
-      <c r="T38" s="24">
+      <c r="T38" s="22">
         <f t="shared" si="7"/>
         <v>2.5862068965517241E-2</v>
       </c>
-      <c r="U38" s="29">
+      <c r="U38" s="27">
         <f t="shared" si="8"/>
-        <v>2.5862068965517242</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2"/>
     </row>
     <row r="39" spans="1:22" ht="37.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="19">
+      <c r="A39" s="17">
         <v>6</v>
       </c>
-      <c r="B39" s="34" t="s">
+      <c r="B39" s="29" t="s">
         <v>300</v>
       </c>
-      <c r="C39" s="32">
-        <v>45722</v>
-      </c>
-      <c r="D39" s="10" t="s">
+      <c r="C39" s="30" t="s">
+        <v>320</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="E39" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="F39" s="10" t="s">
+      <c r="F39" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="G39" s="10" t="s">
+      <c r="G39" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="H39" s="10" t="s">
+      <c r="H39" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="I39" s="10" t="s">
+      <c r="I39" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="J39" s="10" t="s">
+      <c r="J39" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="K39" s="24">
+      <c r="K39" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L39" s="24">
+      <c r="L39" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M39" s="24">
+      <c r="M39" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N39" s="24">
+      <c r="N39" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O39" s="24">
-        <v>100</v>
-      </c>
-      <c r="P39" s="25">
+      <c r="O39" s="22">
+        <v>0</v>
+      </c>
+      <c r="P39" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q39" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R39" s="27">
+      <c r="R39" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S39" s="24">
+        <v>0</v>
+      </c>
+      <c r="S39" s="22">
         <f t="shared" si="16"/>
         <v>0.75</v>
       </c>
-      <c r="T39" s="24">
+      <c r="T39" s="22">
         <f t="shared" si="7"/>
         <v>2.5862068965517241E-2</v>
       </c>
-      <c r="U39" s="29">
+      <c r="U39" s="27">
         <f t="shared" si="8"/>
-        <v>2.5862068965517242</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2"/>
     </row>
     <row r="40" spans="1:22" ht="114.75" x14ac:dyDescent="0.2">
-      <c r="A40" s="19">
+      <c r="A40" s="17">
         <v>6</v>
       </c>
-      <c r="B40" s="34" t="s">
+      <c r="B40" s="29" t="s">
         <v>300</v>
       </c>
-      <c r="C40" s="32">
-        <v>45722</v>
-      </c>
-      <c r="D40" s="10" t="s">
+      <c r="C40" s="30" t="s">
+        <v>320</v>
+      </c>
+      <c r="D40" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="G40" s="7" t="s">
+      <c r="G40" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="H40" s="7" t="s">
+      <c r="H40" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="I40" s="7" t="s">
+      <c r="I40" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="J40" s="7" t="s">
+      <c r="J40" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="K40" s="24">
+      <c r="K40" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L40" s="24">
+      <c r="L40" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M40" s="24">
+      <c r="M40" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N40" s="24">
+      <c r="N40" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O40" s="24">
-        <v>100</v>
-      </c>
-      <c r="P40" s="25">
+      <c r="O40" s="22">
+        <v>2</v>
+      </c>
+      <c r="P40" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q40" s="24">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="Q40" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R40" s="27">
+      <c r="R40" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S40" s="24">
+        <v>3.9215686274509803E-2</v>
+      </c>
+      <c r="S40" s="22">
         <f t="shared" si="16"/>
         <v>0.75</v>
       </c>
-      <c r="T40" s="24">
+      <c r="T40" s="22">
         <f t="shared" si="7"/>
         <v>2.5862068965517241E-2</v>
       </c>
-      <c r="U40" s="29">
+      <c r="U40" s="27">
         <f t="shared" si="8"/>
-        <v>2.5862068965517242</v>
+        <v>5.1724137931034482E-2</v>
       </c>
       <c r="V40" s="2"/>
     </row>
     <row r="41" spans="1:22" ht="51" x14ac:dyDescent="0.2">
-      <c r="A41" s="19">
+      <c r="A41" s="17">
         <v>7</v>
       </c>
-      <c r="B41" s="34" t="s">
+      <c r="B41" s="29" t="s">
         <v>301</v>
       </c>
-      <c r="C41" s="32">
-        <v>45664</v>
-      </c>
-      <c r="D41" s="10" t="s">
+      <c r="C41" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="D41" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E41" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="F41" s="10" t="s">
+      <c r="F41" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="G41" s="10" t="s">
+      <c r="G41" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="H41" s="10" t="s">
+      <c r="H41" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="I41" s="10" t="s">
+      <c r="I41" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="J41" s="10" t="s">
+      <c r="J41" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K41" s="24">
+      <c r="K41" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L41" s="24">
+      <c r="L41" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M41" s="24">
+      <c r="M41" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N41" s="24">
+      <c r="N41" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O41" s="24">
-        <v>100</v>
-      </c>
-      <c r="P41" s="25">
+      <c r="O41" s="22">
+        <v>4</v>
+      </c>
+      <c r="P41" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q41" s="24">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="Q41" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R41" s="27">
+      <c r="R41" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S41" s="24">
+        <v>7.8431372549019607E-2</v>
+      </c>
+      <c r="S41" s="22">
         <f>2/8</f>
         <v>0.25</v>
       </c>
-      <c r="T41" s="24">
+      <c r="T41" s="22">
         <f t="shared" si="7"/>
         <v>8.6206896551724137E-3</v>
       </c>
-      <c r="U41" s="29">
+      <c r="U41" s="27">
         <f t="shared" si="8"/>
-        <v>0.86206896551724133</v>
+        <v>3.4482758620689655E-2</v>
       </c>
       <c r="V41" s="2"/>
     </row>
     <row r="42" spans="1:22" ht="127.5" x14ac:dyDescent="0.2">
-      <c r="A42" s="19">
+      <c r="A42" s="17">
         <v>7</v>
       </c>
-      <c r="B42" s="34" t="s">
+      <c r="B42" s="29" t="s">
         <v>301</v>
       </c>
-      <c r="C42" s="32">
-        <v>45664</v>
-      </c>
-      <c r="D42" s="10" t="s">
+      <c r="C42" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="D42" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="G42" s="7" t="s">
+      <c r="G42" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="H42" s="7" t="s">
+      <c r="H42" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="I42" s="7" t="s">
+      <c r="I42" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="J42" s="7" t="s">
+      <c r="J42" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K42" s="24">
+      <c r="K42" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L42" s="24">
+      <c r="L42" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M42" s="24">
+      <c r="M42" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N42" s="24">
+      <c r="N42" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O42" s="24">
-        <v>100</v>
-      </c>
-      <c r="P42" s="25">
+      <c r="O42" s="22">
+        <v>6</v>
+      </c>
+      <c r="P42" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q42" s="24">
+        <v>0.125</v>
+      </c>
+      <c r="Q42" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R42" s="27">
+      <c r="R42" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S42" s="24">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="S42" s="22">
         <f t="shared" ref="S42:S45" si="18">2/8</f>
         <v>0.25</v>
       </c>
-      <c r="T42" s="24">
+      <c r="T42" s="22">
         <f t="shared" si="7"/>
         <v>8.6206896551724137E-3</v>
       </c>
-      <c r="U42" s="29">
+      <c r="U42" s="27">
         <f t="shared" si="8"/>
-        <v>0.86206896551724133</v>
+        <v>5.1724137931034482E-2</v>
       </c>
       <c r="V42" s="2"/>
     </row>
     <row r="43" spans="1:22" ht="216.75" x14ac:dyDescent="0.2">
-      <c r="A43" s="19">
+      <c r="A43" s="17">
         <v>7</v>
       </c>
-      <c r="B43" s="34" t="s">
+      <c r="B43" s="29" t="s">
         <v>301</v>
       </c>
-      <c r="C43" s="12">
-        <v>45695</v>
-      </c>
-      <c r="D43" s="10" t="s">
+      <c r="C43" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="D43" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="E43" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="F43" s="10" t="s">
+      <c r="F43" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="G43" s="10" t="s">
+      <c r="G43" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="H43" s="10" t="s">
+      <c r="H43" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="I43" s="10" t="s">
+      <c r="I43" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="J43" s="10" t="s">
+      <c r="J43" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K43" s="24">
+      <c r="K43" s="22">
         <v>1</v>
       </c>
-      <c r="L43" s="24">
+      <c r="L43" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M43" s="24">
+      <c r="M43" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N43" s="24">
+      <c r="N43" s="22">
         <f t="shared" si="2"/>
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="O43" s="24">
-        <v>100</v>
-      </c>
-      <c r="P43" s="25">
+      <c r="O43" s="22">
+        <v>8</v>
+      </c>
+      <c r="P43" s="23">
         <f t="shared" si="3"/>
-        <v>4.1666666666666661</v>
-      </c>
-      <c r="Q43" s="24">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Q43" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R43" s="27">
+      <c r="R43" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S43" s="24">
+        <v>0.15686274509803921</v>
+      </c>
+      <c r="S43" s="22">
         <f t="shared" si="18"/>
         <v>0.25</v>
       </c>
-      <c r="T43" s="24">
+      <c r="T43" s="22">
         <f t="shared" si="7"/>
         <v>8.6206896551724137E-3</v>
       </c>
-      <c r="U43" s="29">
+      <c r="U43" s="27">
         <f t="shared" si="8"/>
-        <v>0.86206896551724133</v>
+        <v>6.8965517241379309E-2</v>
       </c>
       <c r="V43" s="2"/>
     </row>
     <row r="44" spans="1:22" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A44" s="19">
+      <c r="A44" s="17">
         <v>7</v>
       </c>
-      <c r="B44" s="34" t="s">
+      <c r="B44" s="29" t="s">
         <v>301</v>
       </c>
-      <c r="C44" s="31">
-        <v>45723</v>
-      </c>
-      <c r="D44" s="7" t="s">
+      <c r="C44" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="D44" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="F44" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="G44" s="7" t="s">
+      <c r="G44" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="H44" s="7" t="s">
+      <c r="H44" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="I44" s="7" t="s">
+      <c r="I44" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="J44" s="7" t="s">
+      <c r="J44" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="K44" s="24">
+      <c r="K44" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L44" s="24">
+      <c r="L44" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M44" s="24">
+      <c r="M44" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N44" s="24">
+      <c r="N44" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O44" s="24">
-        <v>100</v>
-      </c>
-      <c r="P44" s="25">
+      <c r="O44" s="22">
+        <v>10</v>
+      </c>
+      <c r="P44" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q44" s="24">
+        <v>0.20833333333333331</v>
+      </c>
+      <c r="Q44" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R44" s="27">
+      <c r="R44" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S44" s="24">
+        <v>0.19607843137254902</v>
+      </c>
+      <c r="S44" s="22">
         <f t="shared" si="18"/>
         <v>0.25</v>
       </c>
-      <c r="T44" s="24">
+      <c r="T44" s="22">
         <f t="shared" si="7"/>
         <v>8.6206896551724137E-3</v>
       </c>
-      <c r="U44" s="29">
+      <c r="U44" s="27">
         <f t="shared" si="8"/>
-        <v>0.86206896551724133</v>
+        <v>8.6206896551724144E-2</v>
       </c>
       <c r="V44" s="2"/>
     </row>
     <row r="45" spans="1:22" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A45" s="19">
+      <c r="A45" s="17">
         <v>7</v>
       </c>
-      <c r="B45" s="34" t="s">
+      <c r="B45" s="29" t="s">
         <v>301</v>
       </c>
-      <c r="C45" s="31">
-        <v>45723</v>
-      </c>
-      <c r="D45" s="7" t="s">
+      <c r="C45" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="D45" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="E45" s="9" t="s">
+      <c r="E45" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="F45" s="10" t="s">
+      <c r="F45" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="G45" s="10" t="s">
+      <c r="G45" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="H45" s="10" t="s">
+      <c r="H45" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="I45" s="10" t="s">
+      <c r="I45" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="J45" s="10" t="s">
+      <c r="J45" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="K45" s="24">
+      <c r="K45" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L45" s="24">
+      <c r="L45" s="22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="M45" s="24">
+      <c r="M45" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N45" s="24">
+      <c r="N45" s="22">
         <f t="shared" si="2"/>
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O45" s="24">
-        <v>100</v>
-      </c>
-      <c r="P45" s="25">
+      <c r="O45" s="22">
+        <v>12</v>
+      </c>
+      <c r="P45" s="23">
         <f t="shared" si="3"/>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="Q45" s="24">
+        <v>0.25</v>
+      </c>
+      <c r="Q45" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R45" s="27">
+      <c r="R45" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S45" s="24">
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="S45" s="22">
         <f t="shared" si="18"/>
         <v>0.25</v>
       </c>
-      <c r="T45" s="24">
+      <c r="T45" s="22">
         <f t="shared" si="7"/>
         <v>8.6206896551724137E-3</v>
       </c>
-      <c r="U45" s="29">
+      <c r="U45" s="27">
         <f t="shared" si="8"/>
-        <v>0.86206896551724133</v>
+        <v>0.10344827586206896</v>
       </c>
       <c r="V45" s="2"/>
     </row>
     <row r="46" spans="1:22" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A46" s="19">
+      <c r="A46" s="17">
         <v>8</v>
       </c>
-      <c r="B46" s="34" t="s">
+      <c r="B46" s="29" t="s">
         <v>302</v>
       </c>
-      <c r="C46" s="31">
-        <v>45665</v>
-      </c>
-      <c r="D46" s="7" t="s">
+      <c r="C46" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="D46" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="F46" s="13" t="s">
+      <c r="F46" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="G46" s="13" t="s">
+      <c r="G46" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="H46" s="7" t="s">
+      <c r="H46" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="I46" s="7" t="s">
+      <c r="I46" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="J46" s="7" t="s">
+      <c r="J46" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K46" s="24">
+      <c r="K46" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L46" s="24">
+      <c r="L46" s="22">
         <f>1/4</f>
         <v>0.25</v>
       </c>
-      <c r="M46" s="24">
+      <c r="M46" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N46" s="24">
+      <c r="N46" s="22">
         <f t="shared" si="2"/>
         <v>1.5625E-2</v>
       </c>
-      <c r="O46" s="24">
-        <v>100</v>
-      </c>
-      <c r="P46" s="25">
+      <c r="O46" s="22">
+        <v>14</v>
+      </c>
+      <c r="P46" s="23">
         <f t="shared" si="3"/>
-        <v>1.5625</v>
-      </c>
-      <c r="Q46" s="24">
+        <v>0.21875</v>
+      </c>
+      <c r="Q46" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R46" s="27">
+      <c r="R46" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S46" s="24">
+        <v>0.27450980392156865</v>
+      </c>
+      <c r="S46" s="22">
         <f>3/8</f>
         <v>0.375</v>
       </c>
-      <c r="T46" s="24">
+      <c r="T46" s="22">
         <f t="shared" si="7"/>
         <v>1.2931034482758621E-2</v>
       </c>
-      <c r="U46" s="29">
+      <c r="U46" s="27">
         <f t="shared" si="8"/>
-        <v>1.2931034482758621</v>
+        <v>0.18103448275862069</v>
       </c>
       <c r="V46" s="2"/>
     </row>
     <row r="47" spans="1:22" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A47" s="19">
+      <c r="A47" s="17">
         <v>8</v>
       </c>
-      <c r="B47" s="34" t="s">
+      <c r="B47" s="29" t="s">
         <v>302</v>
       </c>
-      <c r="C47" s="31">
-        <v>45665</v>
-      </c>
-      <c r="D47" s="7" t="s">
+      <c r="C47" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="D47" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="E47" s="9" t="s">
+      <c r="E47" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="F47" s="10" t="s">
+      <c r="F47" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="G47" s="10" t="s">
+      <c r="G47" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="H47" s="10" t="s">
+      <c r="H47" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="I47" s="10" t="s">
+      <c r="I47" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="J47" s="10" t="s">
+      <c r="J47" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K47" s="24">
+      <c r="K47" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L47" s="24">
+      <c r="L47" s="22">
         <f t="shared" ref="L47:L52" si="19">1/4</f>
         <v>0.25</v>
       </c>
-      <c r="M47" s="24">
+      <c r="M47" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N47" s="24">
+      <c r="N47" s="22">
         <f t="shared" si="2"/>
         <v>1.5625E-2</v>
       </c>
-      <c r="O47" s="24">
-        <v>100</v>
-      </c>
-      <c r="P47" s="25">
+      <c r="O47" s="22">
+        <v>16</v>
+      </c>
+      <c r="P47" s="23">
         <f t="shared" si="3"/>
-        <v>1.5625</v>
-      </c>
-      <c r="Q47" s="24">
+        <v>0.25</v>
+      </c>
+      <c r="Q47" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R47" s="27">
+      <c r="R47" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S47" s="24">
+        <v>0.31372549019607843</v>
+      </c>
+      <c r="S47" s="22">
         <f t="shared" ref="S47:S52" si="20">3/8</f>
         <v>0.375</v>
       </c>
-      <c r="T47" s="24">
+      <c r="T47" s="22">
         <f t="shared" si="7"/>
         <v>1.2931034482758621E-2</v>
       </c>
-      <c r="U47" s="29">
+      <c r="U47" s="27">
         <f t="shared" si="8"/>
-        <v>1.2931034482758621</v>
+        <v>0.20689655172413793</v>
       </c>
       <c r="V47" s="2"/>
     </row>
     <row r="48" spans="1:22" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A48" s="19">
+      <c r="A48" s="17">
         <v>8</v>
       </c>
-      <c r="B48" s="34" t="s">
+      <c r="B48" s="29" t="s">
         <v>302</v>
       </c>
-      <c r="C48" s="31">
-        <v>45696</v>
-      </c>
-      <c r="D48" s="7" t="s">
+      <c r="C48" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="D48" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E48" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="F48" s="13" t="s">
+      <c r="F48" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="G48" s="13" t="s">
+      <c r="G48" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="H48" s="7" t="s">
+      <c r="H48" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="I48" s="7" t="s">
+      <c r="I48" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="J48" s="7" t="s">
+      <c r="J48" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K48" s="24">
+      <c r="K48" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L48" s="24">
+      <c r="L48" s="22">
         <f t="shared" si="19"/>
         <v>0.25</v>
       </c>
-      <c r="M48" s="24">
+      <c r="M48" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N48" s="24">
+      <c r="N48" s="22">
         <f t="shared" si="2"/>
         <v>1.5625E-2</v>
       </c>
-      <c r="O48" s="24">
-        <v>100</v>
-      </c>
-      <c r="P48" s="25">
+      <c r="O48" s="22">
+        <v>18</v>
+      </c>
+      <c r="P48" s="23">
         <f t="shared" si="3"/>
-        <v>1.5625</v>
-      </c>
-      <c r="Q48" s="24">
+        <v>0.28125</v>
+      </c>
+      <c r="Q48" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R48" s="27">
+      <c r="R48" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S48" s="24">
+        <v>0.3529411764705882</v>
+      </c>
+      <c r="S48" s="22">
         <f t="shared" si="20"/>
         <v>0.375</v>
       </c>
-      <c r="T48" s="24">
+      <c r="T48" s="22">
         <f t="shared" si="7"/>
         <v>1.2931034482758621E-2</v>
       </c>
-      <c r="U48" s="29">
+      <c r="U48" s="27">
         <f t="shared" si="8"/>
-        <v>1.2931034482758621</v>
+        <v>0.23275862068965517</v>
       </c>
       <c r="V48" s="2"/>
     </row>
     <row r="49" spans="1:22" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A49" s="19">
+      <c r="A49" s="17">
         <v>8</v>
       </c>
-      <c r="B49" s="34" t="s">
+      <c r="B49" s="29" t="s">
         <v>302</v>
       </c>
-      <c r="C49" s="31">
-        <v>45696</v>
-      </c>
-      <c r="D49" s="7" t="s">
+      <c r="C49" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="D49" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="E49" s="9" t="s">
+      <c r="E49" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="F49" s="10" t="s">
+      <c r="F49" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="G49" s="10" t="s">
+      <c r="G49" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="H49" s="10" t="s">
+      <c r="H49" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="I49" s="10" t="s">
+      <c r="I49" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="J49" s="10" t="s">
+      <c r="J49" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K49" s="24">
+      <c r="K49" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L49" s="24">
+      <c r="L49" s="22">
         <f t="shared" si="19"/>
         <v>0.25</v>
       </c>
-      <c r="M49" s="24">
+      <c r="M49" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N49" s="24">
+      <c r="N49" s="22">
         <f t="shared" si="2"/>
         <v>1.5625E-2</v>
       </c>
-      <c r="O49" s="24">
-        <v>100</v>
-      </c>
-      <c r="P49" s="25">
+      <c r="O49" s="22">
+        <v>20</v>
+      </c>
+      <c r="P49" s="23">
         <f t="shared" si="3"/>
-        <v>1.5625</v>
-      </c>
-      <c r="Q49" s="24">
+        <v>0.3125</v>
+      </c>
+      <c r="Q49" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R49" s="27">
+      <c r="R49" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S49" s="24">
+        <v>0.39215686274509803</v>
+      </c>
+      <c r="S49" s="22">
         <f t="shared" si="20"/>
         <v>0.375</v>
       </c>
-      <c r="T49" s="24">
+      <c r="T49" s="22">
         <f t="shared" si="7"/>
         <v>1.2931034482758621E-2</v>
       </c>
-      <c r="U49" s="29">
+      <c r="U49" s="27">
         <f t="shared" si="8"/>
-        <v>1.2931034482758621</v>
+        <v>0.25862068965517243</v>
       </c>
       <c r="V49" s="2"/>
     </row>
     <row r="50" spans="1:22" ht="102" x14ac:dyDescent="0.2">
-      <c r="A50" s="19">
+      <c r="A50" s="17">
         <v>8</v>
       </c>
-      <c r="B50" s="34" t="s">
+      <c r="B50" s="29" t="s">
         <v>302</v>
       </c>
-      <c r="C50" s="6">
-        <v>45724</v>
-      </c>
-      <c r="D50" s="7" t="s">
+      <c r="C50" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="D50" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="F50" s="7" t="s">
+      <c r="F50" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="G50" s="7" t="s">
+      <c r="G50" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="H50" s="7" t="s">
+      <c r="H50" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="I50" s="7" t="s">
+      <c r="I50" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="J50" s="7" t="s">
+      <c r="J50" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K50" s="24">
+      <c r="K50" s="22">
         <v>1</v>
       </c>
-      <c r="L50" s="24">
+      <c r="L50" s="22">
         <f t="shared" si="19"/>
         <v>0.25</v>
       </c>
-      <c r="M50" s="24">
+      <c r="M50" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N50" s="24">
+      <c r="N50" s="22">
         <f t="shared" si="2"/>
         <v>3.125E-2</v>
       </c>
-      <c r="O50" s="24">
-        <v>100</v>
-      </c>
-      <c r="P50" s="25">
+      <c r="O50" s="22">
+        <v>0</v>
+      </c>
+      <c r="P50" s="23">
         <f t="shared" si="3"/>
-        <v>3.125</v>
-      </c>
-      <c r="Q50" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R50" s="27">
+      <c r="R50" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S50" s="24">
+        <v>0</v>
+      </c>
+      <c r="S50" s="22">
         <f t="shared" si="20"/>
         <v>0.375</v>
       </c>
-      <c r="T50" s="24">
+      <c r="T50" s="22">
         <f t="shared" si="7"/>
         <v>1.2931034482758621E-2</v>
       </c>
-      <c r="U50" s="29">
+      <c r="U50" s="27">
         <f t="shared" si="8"/>
-        <v>1.2931034482758621</v>
+        <v>0</v>
       </c>
       <c r="V50" s="2"/>
     </row>
     <row r="51" spans="1:22" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A51" s="19">
+      <c r="A51" s="17">
         <v>8</v>
       </c>
-      <c r="B51" s="34" t="s">
+      <c r="B51" s="29" t="s">
         <v>302</v>
       </c>
-      <c r="C51" s="32">
-        <v>45755</v>
-      </c>
-      <c r="D51" s="10" t="s">
+      <c r="C51" s="30" t="s">
+        <v>327</v>
+      </c>
+      <c r="D51" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="E51" s="9" t="s">
+      <c r="E51" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="F51" s="14" t="s">
+      <c r="F51" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="G51" s="14" t="s">
+      <c r="G51" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="H51" s="10" t="s">
+      <c r="H51" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="I51" s="10" t="s">
+      <c r="I51" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="J51" s="10" t="s">
+      <c r="J51" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K51" s="24">
+      <c r="K51" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L51" s="24">
+      <c r="L51" s="22">
         <f t="shared" si="19"/>
         <v>0.25</v>
       </c>
-      <c r="M51" s="24">
+      <c r="M51" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N51" s="24">
+      <c r="N51" s="22">
         <f t="shared" si="2"/>
         <v>1.5625E-2</v>
       </c>
-      <c r="O51" s="24">
-        <v>100</v>
-      </c>
-      <c r="P51" s="25">
+      <c r="O51" s="22">
+        <v>0</v>
+      </c>
+      <c r="P51" s="23">
         <f t="shared" si="3"/>
-        <v>1.5625</v>
-      </c>
-      <c r="Q51" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R51" s="27">
+      <c r="R51" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S51" s="24">
+        <v>0</v>
+      </c>
+      <c r="S51" s="22">
         <f t="shared" si="20"/>
         <v>0.375</v>
       </c>
-      <c r="T51" s="24">
+      <c r="T51" s="22">
         <f t="shared" si="7"/>
         <v>1.2931034482758621E-2</v>
       </c>
-      <c r="U51" s="29">
+      <c r="U51" s="27">
         <f t="shared" si="8"/>
-        <v>1.2931034482758621</v>
+        <v>0</v>
       </c>
       <c r="V51" s="2"/>
     </row>
     <row r="52" spans="1:22" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A52" s="19">
+      <c r="A52" s="17">
         <v>8</v>
       </c>
-      <c r="B52" s="34" t="s">
+      <c r="B52" s="29" t="s">
         <v>302</v>
       </c>
-      <c r="C52" s="32">
-        <v>45755</v>
-      </c>
-      <c r="D52" s="10" t="s">
+      <c r="C52" s="30" t="s">
+        <v>327</v>
+      </c>
+      <c r="D52" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="E52" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="F52" s="13" t="s">
+      <c r="F52" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="G52" s="13" t="s">
+      <c r="G52" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="H52" s="7" t="s">
+      <c r="H52" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="I52" s="7" t="s">
+      <c r="I52" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="J52" s="7" t="s">
+      <c r="J52" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K52" s="24">
+      <c r="K52" s="22">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="L52" s="24">
+      <c r="L52" s="22">
         <f t="shared" si="19"/>
         <v>0.25</v>
       </c>
-      <c r="M52" s="24">
+      <c r="M52" s="22">
         <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
-      <c r="N52" s="24">
+      <c r="N52" s="22">
         <f t="shared" si="2"/>
         <v>1.5625E-2</v>
       </c>
-      <c r="O52" s="24">
-        <v>100</v>
-      </c>
-      <c r="P52" s="25">
+      <c r="O52" s="22">
+        <v>0</v>
+      </c>
+      <c r="P52" s="23">
         <f t="shared" si="3"/>
-        <v>1.5625</v>
-      </c>
-      <c r="Q52" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="22">
         <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
-      <c r="R52" s="27">
+      <c r="R52" s="25">
         <f t="shared" si="5"/>
-        <v>1.9607843137254901</v>
-      </c>
-      <c r="S52" s="24">
+        <v>0</v>
+      </c>
+      <c r="S52" s="22">
         <f t="shared" si="20"/>
         <v>0.375</v>
       </c>
-      <c r="T52" s="24">
+      <c r="T52" s="22">
         <f t="shared" si="7"/>
         <v>1.2931034482758621E-2</v>
       </c>
-      <c r="U52" s="29">
+      <c r="U52" s="27">
         <f t="shared" si="8"/>
-        <v>1.2931034482758621</v>
+        <v>0</v>
       </c>
       <c r="V52" s="2"/>
     </row>
@@ -5412,23 +5486,23 @@
       <c r="O53" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="P53" s="26">
+      <c r="P53" s="24">
         <f>SUM(P2:P52)</f>
-        <v>99.999999999999972</v>
+        <v>7.9722222222222214</v>
       </c>
       <c r="Q53" s="2"/>
-      <c r="R53" s="28">
+      <c r="R53" s="26">
         <f>SUM(R2:R52)</f>
-        <v>99.999999999999872</v>
+        <v>7.901960784313725</v>
       </c>
       <c r="S53" s="2">
         <f>SUM(S2:S52)</f>
         <v>29</v>
       </c>
       <c r="T53" s="2"/>
-      <c r="U53" s="30">
+      <c r="U53" s="28">
         <f>SUM(U2:U52)</f>
-        <v>100.00000000000001</v>
+        <v>6.8146551724137954</v>
       </c>
       <c r="V53" s="2"/>
     </row>
@@ -10560,6 +10634,7 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <autoFilter ref="A1:J53" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.25" right="0.25" top="0.19685039370078738" bottom="0.11811023622047244" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
@@ -10567,30 +10642,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="31067d2d-e48e-4508-aa64-80d1f142e7dc">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ee1a5240-fbb3-422c-a5c8-d7a8e3758d68" xsi:nil="true"/>
-    <Status xmlns="31067d2d-e48e-4508-aa64-80d1f142e7dc" xsi:nil="true"/>
-    <AULA xmlns="31067d2d-e48e-4508-aa64-80d1f142e7dc" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E7EE74678CDAA749BF87014A2B4560BF" ma:contentTypeVersion="16" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="82b2c52b98409cb63e1fc8ee40e85e1b">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="31067d2d-e48e-4508-aa64-80d1f142e7dc" xmlns:ns3="ee1a5240-fbb3-422c-a5c8-d7a8e3758d68" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7b812bcda643b875f52de39510d9d1c3" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E7EE74678CDAA749BF87014A2B4560BF" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d027820d0036d222697a6ff7b3f5c47a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="31067d2d-e48e-4508-aa64-80d1f142e7dc" xmlns:ns3="ee1a5240-fbb3-422c-a5c8-d7a8e3758d68" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a4c4f1818ba5fd5562b618916876c884" ns2:_="" ns3:_="">
     <xsd:import namespace="31067d2d-e48e-4508-aa64-80d1f142e7dc"/>
     <xsd:import namespace="ee1a5240-fbb3-422c-a5c8-d7a8e3758d68"/>
     <xsd:element name="properties">
@@ -10644,7 +10697,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2dab9438-f903-450b-a158-c86bb4a35dfc" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2dab9438-f903-450b-a158-c86bb4a35dfc" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -10729,8 +10782,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -10819,27 +10872,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{418474BE-523A-4CDB-A239-24349A4E0812}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="31067d2d-e48e-4508-aa64-80d1f142e7dc"/>
-    <ds:schemaRef ds:uri="ee1a5240-fbb3-422c-a5c8-d7a8e3758d68"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8BF7EAA-9A79-41CF-B8A6-A283D90A8B74}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="31067d2d-e48e-4508-aa64-80d1f142e7dc">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ee1a5240-fbb3-422c-a5c8-d7a8e3758d68" xsi:nil="true"/>
+    <Status xmlns="31067d2d-e48e-4508-aa64-80d1f142e7dc" xsi:nil="true"/>
+    <AULA xmlns="31067d2d-e48e-4508-aa64-80d1f142e7dc" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{516FC86A-60D5-4914-8CB2-2382756CFBE9}">
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1C88677-4A18-48E3-82F8-2960B117C45A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -10855,4 +10911,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8BF7EAA-9A79-41CF-B8A6-A283D90A8B74}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{418474BE-523A-4CDB-A239-24349A4E0812}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="31067d2d-e48e-4508-aa64-80d1f142e7dc"/>
+    <ds:schemaRef ds:uri="ee1a5240-fbb3-422c-a5c8-d7a8e3758d68"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>